--- a/Employee_Reports_wi52/Wali Mohammed Sabry Q0538.xlsx
+++ b/Employee_Reports_wi52/Wali Mohammed Sabry Q0538.xlsx
@@ -539,20 +539,20 @@
       <c r="E3" s="3" t="inlineStr"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>05-Oct-2025</t>
+          <t>23-Aug-2026</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>05-Oct-2027</t>
+          <t>22-Aug-2028</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>411</v>
+        <v>725</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -585,11 +585,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
